--- a/ascend_test_suite/latest/vLLM_model_list.xlsx
+++ b/ascend_test_suite/latest/vLLM_model_list.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 2 --max-model-len 18432 --no-enable-prefix-caching</t>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 4 --max-model-len 18432 --no-enable-prefix-caching --gpu-memory-utilization 0.98</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/ascend_test_suite/latest/vLLM_model_list.xlsx
+++ b/ascend_test_suite/latest/vLLM_model_list.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 4 --max-model-len 18432 --no-enable-prefix-caching --gpu-memory-utilization 0.98</t>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 4 --max-model-len 18432 --no-enable-prefix-caching --gpu-memory-utilization 0.98 --enforce-eager</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/ascend_test_suite/latest/vLLM_model_list.xlsx
+++ b/ascend_test_suite/latest/vLLM_model_list.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 4 --max-model-len 18432 --no-enable-prefix-caching --gpu-memory-utilization 0.98 --enforce-eager</t>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 2 --max-model-len 18432 --no-enable-prefix-caching --enforce-eager</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/ascend_test_suite/latest/vLLM_model_list.xlsx
+++ b/ascend_test_suite/latest/vLLM_model_list.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 2 --max-model-len 18432 --no-enable-prefix-caching --enforce-eager</t>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 2 --max-model-len 18432 --no-enable-prefix-caching --compilation-config '{\"cudagraph_mode\":\"FULL_DECODE_ONLY\"}'</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/ascend_test_suite/latest/vLLM_model_list.xlsx
+++ b/ascend_test_suite/latest/vLLM_model_list.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 2 --max-model-len 18432 --no-enable-prefix-caching --compilation-config '{\"cudagraph_mode\":\"FULL_DECODE_ONLY\"}'</t>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 2 --max-model-len 32768 --no-enable-prefix-caching --compilation-config '{\"cudagraph_mode\":\"FULL_DECODE_ONLY\"}'</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/ascend_test_suite/latest/vLLM_model_list.xlsx
+++ b/ascend_test_suite/latest/vLLM_model_list.xlsx
@@ -1250,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="33.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1408,47 +1408,26 @@
       <c r="T4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DeepSeek-R1-Distill-Llama-70B</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
+        <is>
+          <t>Qwen3-32B</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>H100</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Llama-70B --served-model-name deepseek --port 28881 -tp 4 --no-enable-prefix-caching</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>长上下文场景可以加上参数--compute-mla-model-as-mha</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="n"/>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/Qwen3-32B/ --served-model-name Qwen3-32B --port 28881 --no-enable-prefix-caching -tp 4 --no-enable-prefix-caching</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qwen3-235B-A22B</t>
+          <t>DeepSeek-R1-Distill-Llama-70B</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
@@ -1458,27 +1437,65 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/Qwen3/Qwen3-235B-A22B --served-model-name deepseek --port 28881 -tp 8 --gpu-memory-utilization 0.98 --no-enable-prefix-caching</t>
-        </is>
-      </c>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Llama-70B --served-model-name deepseek --port 28881 -tp 4 --no-enable-prefix-caching</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>长上下文场景可以加上参数--compute-mla-model-as-mha</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="0" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Qwen3-235B-A22B</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/Qwen3/Qwen3-235B-A22B --served-model-name deepseek --port 28881 -tp 8 --gpu-memory-utilization 0.98 --no-enable-prefix-caching</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>DeepSeek-V4-Flash-w8a8-mtp</t>
         </is>
       </c>
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>910B</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-V4-Flash-w8a8-mtp --max_model_len $((512*1024)) --max-num-batched-tokens 8192 --served-model-name deepseek-v4-flash --gpu-memory-utilization 0.95 --max-num-seqs 16 --data-parallel-size 1 --tensor-parallel-size 8 --enable-expert-parallel --tokenizer-mode deepseek_v4 --tool-call-parser deepseek_v4 --enable-auto-tool-choice --reasoning-parser deepseek_v4 --safetensors-load-strategy 'prefetch' --model-loader-extra-config='{\"enable_multithread_load\": \"true\", \"num_threads\": 128}' --quantization ascend --enable-prefix-caching --port 8000 --block-size 128 --speculative-config '{\"num_speculative_tokens\": 1,\"method\": \"mtp\",\"enforce_eager\": true}' --compilation-config '{\"cudagraph_mode\": \"FULL_DECODE_ONLY\", \"cudagraph_capture_sizes\": [1, 2, 4, 8, 16, 24, 32, 40, 48, 56, 64, 128, 256, 512, 1024, 2048, 4096, 8192]}' --async-scheduling --additional-config '{\"ascend_compilation_config\":{\"enable_npugraph_ex\":true,\"enable_static_kernel\":true},\"enable_cpu_binding\": true,\"enable_dsa_cp\": false,\"multistream_overlap_shared_expert\":true}'</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>Ascend env: OMP_PROC_BIND=false; OMP_NUM_THREADS=10; PYTORCH_NPU_ALLOC_CONF=expandable_segments:True; HCCL_BUFFSIZE=1024; TASK_QUEUE_ENABLE=1; HCCL_OP_EXPANSION_MODE=AIV; ASCEND_MAX_OP_CACHE_SIZE=-1; VLLM_ASCEND_ENABLE_MLAPO=1; TE_PARALLEL_COMPILER=32; VLLM_ASCEND_BALANCE_SCHEDULING=1; PYTHONHASHSEED=0 (LD_PRELOAD/jemalloc omitted: not present in vllm-ascend image)</t>
         </is>

--- a/ascend_test_suite/latest/vLLM_model_list.xlsx
+++ b/ascend_test_suite/latest/vLLM_model_list.xlsx
@@ -1250,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="33.1818181818182" customWidth="1" style="3" min="1" max="1"/>
@@ -1501,6 +1501,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>Qwen3.6-27B</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>H100</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env "CUDA_VISIBLE_DEVICES=0,1,2,3" --env "CUDA_DEVICE_ORDER=PCI_BUS_ID" --network host --ipc=host --shm-size="80g" docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 /home/s_limingge/start_qwen3.6-27b.sh -tp 4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" tooltip="http://docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0" display="docker run --rm --runtime nvidia --gpus all --privileged -v /home/weight:/home/weight --env &quot;CUDA_VISIBLE_DEVICES=0,1,2,3&quot; --env &quot;CUDA_DEVICE_ORDER=PCI_BUS_ID&quot; --network host --ipc=host --shm-size=&quot;80g&quot; docker.xcoresigma.com/docker/vllm/vllm-openai:v0.10.0 --model /home/weight/DeepSeek-R1-Distill-Qwen-32B --served-model-name deepseek --port 28881 -tp 1 --max-model-len 18432 --no-enable-prefix-caching" r:id="rId1"/>
